--- a/source_data/workbooks/Source_Data_Supp_Fig3.xlsx
+++ b/source_data/workbooks/Source_Data_Supp_Fig3.xlsx
@@ -123,16 +123,16 @@
     <t>LNCO2, 321 slides</t>
   </si>
   <si>
-    <t>Gemini 3 Pro (deployed reflector)</t>
-  </si>
-  <si>
-    <t>No reflector</t>
-  </si>
-  <si>
-    <t>pearson, backbone alone (vision)</t>
-  </si>
-  <si>
-    <t>pearson, backbone as TissueLab reflector</t>
+    <t>deployed: Gemini-3-Pro</t>
+  </si>
+  <si>
+    <t>no reflector</t>
+  </si>
+  <si>
+    <t>pearson, LLM alone</t>
+  </si>
+  <si>
+    <t>pearson, as TissueLab reflector</t>
   </si>
   <si>
     <t>pearson, no reflector</t>
@@ -1501,8 +1501,8 @@
     <col min="2" max="2" width="23.7109375" customWidth="1"/>
     <col min="3" max="3" width="60.7109375" customWidth="1"/>
     <col min="4" max="4" width="19.7109375" customWidth="1"/>
-    <col min="5" max="5" width="35.7109375" customWidth="1"/>
-    <col min="6" max="6" width="42.7109375" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="6" max="6" width="33.7109375" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" customWidth="1"/>
     <col min="9" max="10" width="12.7109375" customWidth="1"/>
@@ -2265,10 +2265,10 @@
         <v>0.0408</v>
       </c>
       <c r="N3">
-        <v>-0.2236</v>
+        <v>-0.222</v>
       </c>
       <c r="O3">
-        <v>0.0189</v>
+        <v>0.0192</v>
       </c>
       <c r="P3">
         <v>-0.23</v>
@@ -2318,10 +2318,10 @@
         <v>0.0178</v>
       </c>
       <c r="N4">
-        <v>-0.0583</v>
+        <v>-0.0585</v>
       </c>
       <c r="O4">
-        <v>0.1244</v>
+        <v>0.1221</v>
       </c>
       <c r="P4">
         <v>-0.0675</v>
@@ -2371,10 +2371,10 @@
         <v>0.0323</v>
       </c>
       <c r="N5">
-        <v>-0.01</v>
+        <v>-0.0121</v>
       </c>
       <c r="O5">
-        <v>0.1342</v>
+        <v>0.1355</v>
       </c>
       <c r="P5">
         <v>-0.0195</v>
